--- a/artfynd/A 15084-2024 artfynd.xlsx
+++ b/artfynd/A 15084-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121171416</v>
+        <v>121171256</v>
       </c>
       <c r="B2" t="n">
-        <v>100337</v>
+        <v>105099</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>222498</v>
+        <v>221141</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Gullviva</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Primula veris</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>547804</v>
+        <v>547635</v>
       </c>
       <c r="R2" t="n">
-        <v>6346453</v>
+        <v>6346591</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -745,17 +745,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2024-05-29</t>
+          <t>2024-05-31</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2024-05-29</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Välspridd</t>
+          <t>2024-05-31</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -786,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121171255</v>
+        <v>121171240</v>
       </c>
       <c r="B3" t="n">
-        <v>100337</v>
+        <v>100347</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -826,10 +821,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>547635</v>
+        <v>547538</v>
       </c>
       <c r="R3" t="n">
-        <v>6346591</v>
+        <v>6346689</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -892,10 +887,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121171413</v>
+        <v>121171416</v>
       </c>
       <c r="B4" t="n">
-        <v>74517</v>
+        <v>100347</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -908,21 +903,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6428</v>
+        <v>222498</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Rostfläck</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Arthonia vinosa</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Leight.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -932,10 +927,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>547785</v>
+        <v>547804</v>
       </c>
       <c r="R4" t="n">
-        <v>6346456</v>
+        <v>6346453</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -972,7 +967,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>På grov ek</t>
+          <t>Välspridd</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1006,7 +1001,7 @@
         <v>121171419</v>
       </c>
       <c r="B5" t="n">
-        <v>56659</v>
+        <v>56662</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1114,10 +1109,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121171256</v>
+        <v>121171413</v>
       </c>
       <c r="B6" t="n">
-        <v>105089</v>
+        <v>74520</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1130,21 +1125,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>221141</v>
+        <v>6428</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Gullviva</t>
+          <t>Rostfläck</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Primula veris</t>
+          <t>Arthonia vinosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Leight.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1154,10 +1149,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>547635</v>
+        <v>547785</v>
       </c>
       <c r="R6" t="n">
-        <v>6346591</v>
+        <v>6346456</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1184,12 +1179,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2024-05-31</t>
+          <t>2024-05-29</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2024-05-31</t>
+          <t>2024-05-29</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>På grov ek</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1220,10 +1220,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121171240</v>
+        <v>121171255</v>
       </c>
       <c r="B7" t="n">
-        <v>100337</v>
+        <v>100347</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1260,10 +1260,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>547538</v>
+        <v>547635</v>
       </c>
       <c r="R7" t="n">
-        <v>6346689</v>
+        <v>6346591</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>

--- a/artfynd/A 15084-2024 artfynd.xlsx
+++ b/artfynd/A 15084-2024 artfynd.xlsx
@@ -781,7 +781,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121171240</v>
+        <v>121171416</v>
       </c>
       <c r="B3" t="n">
         <v>100347</v>
@@ -821,10 +821,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>547538</v>
+        <v>547804</v>
       </c>
       <c r="R3" t="n">
-        <v>6346689</v>
+        <v>6346453</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -851,12 +851,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2024-05-31</t>
+          <t>2024-05-29</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2024-05-31</t>
+          <t>2024-05-29</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Välspridd</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -887,10 +892,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121171416</v>
+        <v>121171413</v>
       </c>
       <c r="B4" t="n">
-        <v>100347</v>
+        <v>74520</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -903,21 +908,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>222498</v>
+        <v>6428</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Rostfläck</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Arthonia vinosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>Leight.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -927,10 +932,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>547804</v>
+        <v>547785</v>
       </c>
       <c r="R4" t="n">
-        <v>6346453</v>
+        <v>6346456</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -967,7 +972,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Välspridd</t>
+          <t>På grov ek</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1109,10 +1114,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121171413</v>
+        <v>121171240</v>
       </c>
       <c r="B6" t="n">
-        <v>74520</v>
+        <v>100347</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1125,21 +1130,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6428</v>
+        <v>222498</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Rostfläck</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Arthonia vinosa</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Leight.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1149,10 +1154,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>547785</v>
+        <v>547538</v>
       </c>
       <c r="R6" t="n">
-        <v>6346456</v>
+        <v>6346689</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1179,17 +1184,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2024-05-29</t>
+          <t>2024-05-31</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2024-05-29</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>På grov ek</t>
+          <t>2024-05-31</t>
         </is>
       </c>
       <c r="AD6" t="b">

--- a/artfynd/A 15084-2024 artfynd.xlsx
+++ b/artfynd/A 15084-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121171256</v>
+        <v>121171419</v>
       </c>
       <c r="B2" t="n">
-        <v>105099</v>
+        <v>56662</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,37 +691,42 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>221141</v>
+        <v>100038</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Gullviva</t>
+          <t>Skogsduva</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Primula veris</t>
+          <t>Columba oenas</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Gällingsbotrakten, Sm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>547635</v>
+        <v>547805</v>
       </c>
       <c r="R2" t="n">
-        <v>6346591</v>
+        <v>6346447</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -745,12 +750,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2024-05-31</t>
+          <t>2024-05-29</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2024-05-31</t>
+          <t>2024-05-29</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -781,10 +786,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121171416</v>
+        <v>121171256</v>
       </c>
       <c r="B3" t="n">
-        <v>100347</v>
+        <v>105112</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -797,21 +802,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>222498</v>
+        <v>221141</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Gullviva</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Primula veris</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -821,10 +826,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>547804</v>
+        <v>547635</v>
       </c>
       <c r="R3" t="n">
-        <v>6346453</v>
+        <v>6346591</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -851,17 +856,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2024-05-29</t>
+          <t>2024-05-31</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2024-05-29</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Välspridd</t>
+          <t>2024-05-31</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -892,10 +892,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121171413</v>
+        <v>121171416</v>
       </c>
       <c r="B4" t="n">
-        <v>74520</v>
+        <v>100360</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -908,21 +908,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6428</v>
+        <v>222498</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Rostfläck</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Arthonia vinosa</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Leight.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -932,10 +932,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>547785</v>
+        <v>547804</v>
       </c>
       <c r="R4" t="n">
-        <v>6346456</v>
+        <v>6346453</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -972,7 +972,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>På grov ek</t>
+          <t>Välspridd</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1003,10 +1003,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121171419</v>
+        <v>121171413</v>
       </c>
       <c r="B5" t="n">
-        <v>56662</v>
+        <v>74522</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1019,42 +1019,37 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100038</v>
+        <v>6428</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Skogsduva</t>
+          <t>Rostfläck</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Columba oenas</t>
+          <t>Arthonia vinosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>Leight.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Gällingsbotrakten, Sm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>547805</v>
+        <v>547785</v>
       </c>
       <c r="R5" t="n">
-        <v>6346447</v>
+        <v>6346456</v>
       </c>
       <c r="S5" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1084,6 +1079,11 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2024-05-29</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>På grov ek</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1114,10 +1114,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121171240</v>
+        <v>121171255</v>
       </c>
       <c r="B6" t="n">
-        <v>100347</v>
+        <v>100360</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1154,10 +1154,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>547538</v>
+        <v>547635</v>
       </c>
       <c r="R6" t="n">
-        <v>6346689</v>
+        <v>6346591</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1220,10 +1220,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121171255</v>
+        <v>121171240</v>
       </c>
       <c r="B7" t="n">
-        <v>100347</v>
+        <v>100360</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1260,10 +1260,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>547635</v>
+        <v>547538</v>
       </c>
       <c r="R7" t="n">
-        <v>6346591</v>
+        <v>6346689</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>

--- a/artfynd/A 15084-2024 artfynd.xlsx
+++ b/artfynd/A 15084-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121171419</v>
+        <v>121171256</v>
       </c>
       <c r="B2" t="n">
-        <v>56662</v>
+        <v>105113</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,42 +691,37 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100038</v>
+        <v>221141</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Skogsduva</t>
+          <t>Gullviva</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Columba oenas</t>
+          <t>Primula veris</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Gällingsbotrakten, Sm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>547805</v>
+        <v>547635</v>
       </c>
       <c r="R2" t="n">
-        <v>6346447</v>
+        <v>6346591</v>
       </c>
       <c r="S2" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -750,12 +745,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2024-05-29</t>
+          <t>2024-05-31</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2024-05-29</t>
+          <t>2024-05-31</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -786,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121171256</v>
+        <v>121171416</v>
       </c>
       <c r="B3" t="n">
-        <v>105112</v>
+        <v>100361</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -802,21 +797,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>221141</v>
+        <v>222498</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Gullviva</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Primula veris</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -826,10 +821,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>547635</v>
+        <v>547804</v>
       </c>
       <c r="R3" t="n">
-        <v>6346591</v>
+        <v>6346453</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -856,12 +851,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2024-05-31</t>
+          <t>2024-05-29</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2024-05-31</t>
+          <t>2024-05-29</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Välspridd</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -892,10 +892,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121171416</v>
+        <v>121171240</v>
       </c>
       <c r="B4" t="n">
-        <v>100360</v>
+        <v>100361</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -932,10 +932,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>547804</v>
+        <v>547538</v>
       </c>
       <c r="R4" t="n">
-        <v>6346453</v>
+        <v>6346689</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -962,17 +962,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2024-05-29</t>
+          <t>2024-05-31</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2024-05-29</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Välspridd</t>
+          <t>2024-05-31</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1003,10 +998,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121171413</v>
+        <v>121171419</v>
       </c>
       <c r="B5" t="n">
-        <v>74522</v>
+        <v>56662</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1019,37 +1014,42 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6428</v>
+        <v>100038</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Rostfläck</t>
+          <t>Skogsduva</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Arthonia vinosa</t>
+          <t>Columba oenas</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Leight.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Gällingsbotrakten, Sm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>547785</v>
+        <v>547805</v>
       </c>
       <c r="R5" t="n">
-        <v>6346456</v>
+        <v>6346447</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1079,11 +1079,6 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2024-05-29</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>På grov ek</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1114,10 +1109,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121171255</v>
+        <v>121171413</v>
       </c>
       <c r="B6" t="n">
-        <v>100360</v>
+        <v>74522</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1130,21 +1125,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>222498</v>
+        <v>6428</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Rostfläck</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Arthonia vinosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>Leight.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1154,10 +1149,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>547635</v>
+        <v>547785</v>
       </c>
       <c r="R6" t="n">
-        <v>6346591</v>
+        <v>6346456</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1184,12 +1179,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2024-05-31</t>
+          <t>2024-05-29</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2024-05-31</t>
+          <t>2024-05-29</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>På grov ek</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1220,10 +1220,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121171240</v>
+        <v>121171255</v>
       </c>
       <c r="B7" t="n">
-        <v>100360</v>
+        <v>100361</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1260,10 +1260,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>547538</v>
+        <v>547635</v>
       </c>
       <c r="R7" t="n">
-        <v>6346689</v>
+        <v>6346591</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>

--- a/artfynd/A 15084-2024 artfynd.xlsx
+++ b/artfynd/A 15084-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121171256</v>
+        <v>121171240</v>
       </c>
       <c r="B2" t="n">
-        <v>105113</v>
+        <v>100364</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>221141</v>
+        <v>222498</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Gullviva</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Primula veris</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>547635</v>
+        <v>547538</v>
       </c>
       <c r="R2" t="n">
-        <v>6346591</v>
+        <v>6346689</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -781,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121171416</v>
+        <v>121171419</v>
       </c>
       <c r="B3" t="n">
-        <v>100361</v>
+        <v>56665</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -797,37 +797,42 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>222498</v>
+        <v>100038</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Skogsduva</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Columba oenas</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Gällingsbotrakten, Sm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>547804</v>
+        <v>547805</v>
       </c>
       <c r="R3" t="n">
-        <v>6346453</v>
+        <v>6346447</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -857,11 +862,6 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2024-05-29</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Välspridd</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -892,10 +892,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121171240</v>
+        <v>121171256</v>
       </c>
       <c r="B4" t="n">
-        <v>100361</v>
+        <v>105116</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -908,21 +908,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>222498</v>
+        <v>221141</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Gullviva</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Primula veris</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -932,10 +932,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>547538</v>
+        <v>547635</v>
       </c>
       <c r="R4" t="n">
-        <v>6346689</v>
+        <v>6346591</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -998,10 +998,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121171419</v>
+        <v>121171416</v>
       </c>
       <c r="B5" t="n">
-        <v>56662</v>
+        <v>100364</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1014,42 +1014,37 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100038</v>
+        <v>222498</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Skogsduva</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Columba oenas</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Gällingsbotrakten, Sm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>547805</v>
+        <v>547804</v>
       </c>
       <c r="R5" t="n">
-        <v>6346447</v>
+        <v>6346453</v>
       </c>
       <c r="S5" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1079,6 +1074,11 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2024-05-29</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Välspridd</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1112,7 +1112,7 @@
         <v>121171413</v>
       </c>
       <c r="B6" t="n">
-        <v>74522</v>
+        <v>74525</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1223,7 +1223,7 @@
         <v>121171255</v>
       </c>
       <c r="B7" t="n">
-        <v>100361</v>
+        <v>100364</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>

--- a/artfynd/A 15084-2024 artfynd.xlsx
+++ b/artfynd/A 15084-2024 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121171240</v>
+        <v>121171255</v>
       </c>
       <c r="B2" t="n">
         <v>100364</v>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>547538</v>
+        <v>547635</v>
       </c>
       <c r="R2" t="n">
-        <v>6346689</v>
+        <v>6346591</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -781,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121171419</v>
+        <v>121171256</v>
       </c>
       <c r="B3" t="n">
-        <v>56665</v>
+        <v>105116</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -797,42 +797,37 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100038</v>
+        <v>221141</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Skogsduva</t>
+          <t>Gullviva</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Columba oenas</t>
+          <t>Primula veris</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Gällingsbotrakten, Sm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>547805</v>
+        <v>547635</v>
       </c>
       <c r="R3" t="n">
-        <v>6346447</v>
+        <v>6346591</v>
       </c>
       <c r="S3" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -856,12 +851,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2024-05-29</t>
+          <t>2024-05-31</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2024-05-29</t>
+          <t>2024-05-31</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -892,10 +887,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121171256</v>
+        <v>121171413</v>
       </c>
       <c r="B4" t="n">
-        <v>105116</v>
+        <v>74525</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -908,21 +903,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>221141</v>
+        <v>6428</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Gullviva</t>
+          <t>Rostfläck</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Primula veris</t>
+          <t>Arthonia vinosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Leight.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -932,10 +927,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>547635</v>
+        <v>547785</v>
       </c>
       <c r="R4" t="n">
-        <v>6346591</v>
+        <v>6346456</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -962,12 +957,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2024-05-31</t>
+          <t>2024-05-29</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2024-05-31</t>
+          <t>2024-05-29</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>På grov ek</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -998,7 +998,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121171416</v>
+        <v>121171240</v>
       </c>
       <c r="B5" t="n">
         <v>100364</v>
@@ -1038,10 +1038,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>547804</v>
+        <v>547538</v>
       </c>
       <c r="R5" t="n">
-        <v>6346453</v>
+        <v>6346689</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1068,17 +1068,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2024-05-29</t>
+          <t>2024-05-31</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2024-05-29</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Välspridd</t>
+          <t>2024-05-31</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1109,10 +1104,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121171413</v>
+        <v>121171419</v>
       </c>
       <c r="B6" t="n">
-        <v>74525</v>
+        <v>56665</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1125,37 +1120,42 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6428</v>
+        <v>100038</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Rostfläck</t>
+          <t>Skogsduva</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Arthonia vinosa</t>
+          <t>Columba oenas</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Leight.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Gällingsbotrakten, Sm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>547785</v>
+        <v>547805</v>
       </c>
       <c r="R6" t="n">
-        <v>6346456</v>
+        <v>6346447</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1185,11 +1185,6 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2024-05-29</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>På grov ek</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1220,7 +1215,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121171255</v>
+        <v>121171416</v>
       </c>
       <c r="B7" t="n">
         <v>100364</v>
@@ -1260,10 +1255,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>547635</v>
+        <v>547804</v>
       </c>
       <c r="R7" t="n">
-        <v>6346591</v>
+        <v>6346453</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1290,12 +1285,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2024-05-31</t>
+          <t>2024-05-29</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2024-05-31</t>
+          <t>2024-05-29</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Välspridd</t>
         </is>
       </c>
       <c r="AD7" t="b">

--- a/artfynd/A 15084-2024 artfynd.xlsx
+++ b/artfynd/A 15084-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121171255</v>
+        <v>121171240</v>
       </c>
       <c r="B2" t="n">
-        <v>100364</v>
+        <v>100370</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>547635</v>
+        <v>547538</v>
       </c>
       <c r="R2" t="n">
-        <v>6346591</v>
+        <v>6346689</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -784,7 +784,7 @@
         <v>121171256</v>
       </c>
       <c r="B3" t="n">
-        <v>105116</v>
+        <v>105122</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -890,7 +890,7 @@
         <v>121171413</v>
       </c>
       <c r="B4" t="n">
-        <v>74525</v>
+        <v>74526</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -998,10 +998,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121171240</v>
+        <v>121171416</v>
       </c>
       <c r="B5" t="n">
-        <v>100364</v>
+        <v>100370</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1038,10 +1038,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>547538</v>
+        <v>547804</v>
       </c>
       <c r="R5" t="n">
-        <v>6346689</v>
+        <v>6346453</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1068,12 +1068,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2024-05-31</t>
+          <t>2024-05-29</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2024-05-31</t>
+          <t>2024-05-29</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Välspridd</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1107,7 +1112,7 @@
         <v>121171419</v>
       </c>
       <c r="B6" t="n">
-        <v>56665</v>
+        <v>56666</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1215,10 +1220,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121171416</v>
+        <v>121171255</v>
       </c>
       <c r="B7" t="n">
-        <v>100364</v>
+        <v>100370</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1255,10 +1260,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>547804</v>
+        <v>547635</v>
       </c>
       <c r="R7" t="n">
-        <v>6346453</v>
+        <v>6346591</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1285,17 +1290,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2024-05-29</t>
+          <t>2024-05-31</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2024-05-29</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Välspridd</t>
+          <t>2024-05-31</t>
         </is>
       </c>
       <c r="AD7" t="b">
